--- a/xlsx/rgf_despesa_pessoal_PE_2024_2026.xlsx
+++ b/xlsx/rgf_despesa_pessoal_PE_2024_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/021994c2887a2fd0/Documents/Claude/SICONVI/publicacao/rgf-despesa-pessoal/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DB81845FD349A9C614C9E272A4C8551FE70D3134" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_5A83845FD349A9C614C9E272A4C8551F57000B58" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
